--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted_Boot.xlsx
@@ -385,10 +385,10 @@
         <v>15.521</v>
       </c>
       <c r="C2">
-        <v>15.331</v>
+        <v>15.328</v>
       </c>
       <c r="D2">
-        <v>15.718</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="3">
@@ -399,10 +399,10 @@
         <v>8.148</v>
       </c>
       <c r="C3">
-        <v>7.986</v>
+        <v>7.991</v>
       </c>
       <c r="D3">
-        <v>8.316000000000001</v>
+        <v>8.31</v>
       </c>
     </row>
   </sheetData>
@@ -445,10 +445,10 @@
         <v>16.01</v>
       </c>
       <c r="C2">
-        <v>15.809</v>
+        <v>15.816</v>
       </c>
       <c r="D2">
-        <v>16.208</v>
+        <v>16.211</v>
       </c>
     </row>
     <row r="3">
@@ -459,10 +459,10 @@
         <v>8.404</v>
       </c>
       <c r="C3">
-        <v>8.236000000000001</v>
+        <v>8.239000000000001</v>
       </c>
       <c r="D3">
-        <v>8.566000000000001</v>
+        <v>8.57</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted_Boot.xlsx
@@ -382,13 +382,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>15.521</v>
+        <v>13.929</v>
       </c>
       <c r="C2">
-        <v>15.328</v>
+        <v>13.713</v>
       </c>
       <c r="D2">
-        <v>15.71</v>
+        <v>14.146</v>
       </c>
     </row>
     <row r="3">
@@ -396,13 +396,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.148</v>
+        <v>7.469</v>
       </c>
       <c r="C3">
-        <v>7.991</v>
+        <v>7.289</v>
       </c>
       <c r="D3">
-        <v>8.31</v>
+        <v>7.647</v>
       </c>
     </row>
   </sheetData>
@@ -442,13 +442,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16.01</v>
+        <v>14.525</v>
       </c>
       <c r="C2">
-        <v>15.816</v>
+        <v>14.314</v>
       </c>
       <c r="D2">
-        <v>16.211</v>
+        <v>14.738</v>
       </c>
     </row>
     <row r="3">
@@ -456,13 +456,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.404</v>
+        <v>7.789</v>
       </c>
       <c r="C3">
-        <v>8.239000000000001</v>
+        <v>7.599</v>
       </c>
       <c r="D3">
-        <v>8.57</v>
+        <v>7.974</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted_Boot.xlsx
@@ -382,13 +382,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>13.929</v>
+        <v>15.414</v>
       </c>
       <c r="C2">
-        <v>13.713</v>
+        <v>15.222</v>
       </c>
       <c r="D2">
-        <v>14.146</v>
+        <v>15.609</v>
       </c>
     </row>
     <row r="3">
@@ -396,13 +396,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.469</v>
+        <v>8.069000000000001</v>
       </c>
       <c r="C3">
-        <v>7.289</v>
+        <v>7.897</v>
       </c>
       <c r="D3">
-        <v>7.647</v>
+        <v>8.231999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -442,13 +442,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>14.525</v>
+        <v>15.844</v>
       </c>
       <c r="C2">
-        <v>14.314</v>
+        <v>15.644</v>
       </c>
       <c r="D2">
-        <v>14.738</v>
+        <v>16.043</v>
       </c>
     </row>
     <row r="3">
@@ -456,13 +456,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.789</v>
+        <v>8.292999999999999</v>
       </c>
       <c r="C3">
-        <v>7.599</v>
+        <v>8.132999999999999</v>
       </c>
       <c r="D3">
-        <v>7.974</v>
+        <v>8.459</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted_Boot.xlsx
@@ -1,22 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/OMOP Analysis/Results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_35A8F189CA972E91CA412694A5594A1C8451FD1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="boot_all_summary_stats" sheetId="1" r:id="rId1"/>
     <sheet name="boot_user_summary_stats" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+  <si>
+    <t>year_after_index</t>
+  </si>
+  <si>
+    <t>mean_boot_visits</t>
+  </si>
+  <si>
+    <t>lower_ci</t>
+  </si>
+  <si>
+    <t>upper_ci</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,13 +87,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -108,7 +139,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -142,6 +173,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -176,9 +208,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -351,33 +384,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>year_after_index</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>mean_boot_visits</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>lower_ci</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>upper_ci</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -391,18 +416,18 @@
         <v>15.609</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.069000000000001</v>
+        <v>8.0690000000000008</v>
       </c>
       <c r="C3">
-        <v>7.897</v>
+        <v>7.8970000000000002</v>
       </c>
       <c r="D3">
-        <v>8.231999999999999</v>
+        <v>8.2319999999999993</v>
       </c>
     </row>
   </sheetData>
@@ -411,58 +436,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>year_after_index</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>mean_boot_visits</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>lower_ci</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>upper_ci</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>15.844</v>
+        <v>15.843999999999999</v>
       </c>
       <c r="C2">
         <v>15.644</v>
       </c>
       <c r="D2">
-        <v>16.043</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>16.042999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.292999999999999</v>
+        <v>8.2929999999999993</v>
       </c>
       <c r="C3">
-        <v>8.132999999999999</v>
+        <v>8.1329999999999991</v>
       </c>
       <c r="D3">
-        <v>8.459</v>
+        <v>8.4589999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted_Boot.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_visits_OMOP-Unadjusted_Boot.xlsx
@@ -1,45 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/OMOP Analysis/Results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_35A8F189CA972E91CA412694A5594A1C8451FD1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="boot_all_summary_stats" sheetId="1" r:id="rId1"/>
     <sheet name="boot_user_summary_stats" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
-  <si>
-    <t>year_after_index</t>
-  </si>
-  <si>
-    <t>mean_boot_visits</t>
-  </si>
-  <si>
-    <t>lower_ci</t>
-  </si>
-  <si>
-    <t>upper_ci</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,21 +64,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -139,7 +108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -173,7 +142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -208,10 +176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -384,50 +351,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>year_after_index</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>mean_boot_visits</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>lower_ci</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>upper_ci</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>15.414</v>
+        <v>112.794</v>
       </c>
       <c r="C2">
-        <v>15.222</v>
+        <v>111.429</v>
       </c>
       <c r="D2">
-        <v>15.609</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>114.202</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.0690000000000008</v>
+        <v>53.881</v>
       </c>
       <c r="C3">
-        <v>7.8970000000000002</v>
+        <v>52.715</v>
       </c>
       <c r="D3">
-        <v>8.2319999999999993</v>
+        <v>55.012</v>
       </c>
     </row>
   </sheetData>
@@ -436,50 +411,58 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>year_after_index</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>mean_boot_visits</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>lower_ci</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>upper_ci</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>15.843999999999999</v>
+        <v>60.298</v>
       </c>
       <c r="C2">
-        <v>15.644</v>
+        <v>59.473</v>
       </c>
       <c r="D2">
-        <v>16.042999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>61.093</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>8.2929999999999993</v>
+        <v>33.179</v>
       </c>
       <c r="C3">
-        <v>8.1329999999999991</v>
+        <v>32.499</v>
       </c>
       <c r="D3">
-        <v>8.4589999999999996</v>
+        <v>33.853</v>
       </c>
     </row>
   </sheetData>
